--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>706522.6153393454</v>
+        <v>706523</v>
       </c>
       <c r="R2" t="n">
-        <v>6352249.122605586</v>
+        <v>6352249</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1987-07-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105606</v>
+        <v>105615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105615</v>
+        <v>105627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105627</v>
+        <v>105636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105636</v>
+        <v>105639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105639</v>
+        <v>105667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105667</v>
+        <v>105673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105673</v>
+        <v>105680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105684</v>
+        <v>105691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105694</v>
+        <v>105699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44619-2025 artfynd.xlsx
+++ b/artfynd/A 44619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450379</v>
       </c>
       <c r="B2" t="n">
-        <v>105699</v>
+        <v>105707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
